--- a/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0023.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0023.xlsx
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Vào Phòng Điều Chỉnh</t>
+          <t>Vào Phòng Modulation</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Return Đại Sảnh Điều Chỉnh</t>
+          <t>Return Đại Sảnh Modulation</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Return Đại Sảnh Điều Chỉnh</t>
+          <t>Return Đại Sảnh Modulation</t>
         </is>
       </c>
     </row>
